--- a/docs/REPAIR01_20260823/SIDEBAR_LAYER_MAP.xlsx
+++ b/docs/REPAIR01_20260823/SIDEBAR_LAYER_MAP.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">89</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">80</t>
+          <t xml:space="preserve">81</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189</t>
+          <t xml:space="preserve">1192</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">323</t>
+          <t xml:space="preserve">325</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">400</t>
+          <t xml:space="preserve">401</t>
         </is>
       </c>
     </row>
@@ -5948,32 +5948,32 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×2)</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×3)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">تسجيل التايم شيت والإنتاج</t>
+          <t xml:space="preserve">قرارات الهيكل التنظيمي</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">timesheet/view_timesheet</t>
+          <t xml:space="preserve">portal/ceo_org_decisions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
+          <t xml:space="preserve">ورقةُ EX-CEO — مساحة الرئيس التنفيذي</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
+          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
         </is>
       </c>
     </row>
@@ -5990,17 +5990,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×2)</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×3)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">أوامر الصيانة</t>
+          <t xml:space="preserve">تسجيل التايم شيت والإنتاج</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">maintenance/orders</t>
+          <t xml:space="preserve">timesheet/view_timesheet</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -6032,17 +6032,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×2)</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×3)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">غرفة عمليات المواقع</t>
+          <t xml:space="preserve">أوامر الصيانة</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">operations/operations_room</t>
+          <t xml:space="preserve">maintenance/orders</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -6074,17 +6074,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×2)</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×3)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">تصحيح الوحدات بالسلسلة الثلاثية</t>
+          <t xml:space="preserve">غرفة عمليات المواقع</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">operations/unit_correction</t>
+          <t xml:space="preserve">operations/operations_room</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6116,17 +6116,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×2)</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×3)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">الأداء الشهري للوحدة</t>
+          <t xml:space="preserve">تصحيح الوحدات بالسلسلة الثلاثية</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">operations/unit_perf</t>
+          <t xml:space="preserve">operations/unit_correction</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6158,17 +6158,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×2)</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×3)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">طلب تبديل</t>
+          <t xml:space="preserve">الأداء الشهري للوحدة</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">operations/swap_request</t>
+          <t xml:space="preserve">operations/unit_perf</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6200,32 +6200,32 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×2)</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×3)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">طلب الترحيل</t>
+          <t xml:space="preserve">طلب تبديل</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">transport/transfer_requests</t>
+          <t xml:space="preserve">operations/swap_request</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">ورقةُ DEP-15 — إدارة النقل والترحيل</t>
+          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
+          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
         </is>
       </c>
     </row>
@@ -6242,12 +6242,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×2)</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×3)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">طلبات الترحيل</t>
+          <t xml:space="preserve">طلب الترحيل</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -6284,32 +6284,32 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×2)</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×3)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">إسناد المعدات للوحدات</t>
+          <t xml:space="preserve">طلبات الترحيل</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">operations/containers</t>
+          <t xml:space="preserve">transport/transfer_requests</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
+          <t xml:space="preserve">ورقةُ DEP-15 — إدارة النقل والترحيل</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
+          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
         </is>
       </c>
     </row>
@@ -6326,17 +6326,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×2)</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×3)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">تكليف المشغل على المعدة</t>
+          <t xml:space="preserve">إسناد المعدات للوحدات</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">operations/distribution_space</t>
+          <t xml:space="preserve">operations/containers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6368,17 +6368,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×2)</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×3)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">الإنتاج والقياس</t>
+          <t xml:space="preserve">تكليف المشغل على المعدة</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">operations/production</t>
+          <t xml:space="preserve">operations/distribution_space</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -6410,17 +6410,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×2)</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×3)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">التوقفات وتحديد المتحمل</t>
+          <t xml:space="preserve">الإنتاج والقياس</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">operations/stops_unattributed</t>
+          <t xml:space="preserve">operations/production</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -6447,22 +6447,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">العقود والعملاء</t>
+          <t xml:space="preserve">التشغيل اليومي</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×3 + ④ ×2)</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×10 + ④ ×3)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">الجزاءات والحوافز التعاقدية</t>
+          <t xml:space="preserve">التوقفات وتحديد المتحمل</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">contracts/penalties</t>
+          <t xml:space="preserve">operations/stops_unattributed</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -6499,27 +6499,27 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">سجل عقود المشاريع</t>
+          <t xml:space="preserve">الجزاءات والحوافز التعاقدية</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">contracts/contracts</t>
+          <t xml:space="preserve">contracts/penalties</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ورقةُ DEP-01 — إدارة المبيعات التعاقدية والعقود</t>
+          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
+          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
         </is>
       </c>
     </row>
@@ -6541,27 +6541,27 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">توزيع وحدات المورد على معداته</t>
+          <t xml:space="preserve">سجل عقود المشاريع</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">operations/equipment_quota</t>
+          <t xml:space="preserve">contracts/contracts</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
+          <t xml:space="preserve">ورقةُ DEP-01 — إدارة المبيعات التعاقدية والعقود</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
+          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
         </is>
       </c>
     </row>
@@ -6583,27 +6583,27 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">المطالبات والتسليم للمالية</t>
+          <t xml:space="preserve">توزيع وحدات المورد على معداته</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">contracts/claims</t>
+          <t xml:space="preserve">operations/equipment_quota</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">ورقةُ DEP-01 — إدارة المبيعات التعاقدية والعقود</t>
+          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
+          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
         </is>
       </c>
     </row>
@@ -6625,27 +6625,27 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">الأعمال غير المفوترة</t>
+          <t xml:space="preserve">المطالبات والتسليم للمالية</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">operations/unbilled</t>
+          <t xml:space="preserve">contracts/claims</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
+          <t xml:space="preserve">ورقةُ DEP-01 — إدارة المبيعات التعاقدية والعقود</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
+          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
         </is>
       </c>
     </row>
@@ -6657,37 +6657,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">الموظفون والمشغلون</t>
+          <t xml:space="preserve">العقود والعملاء</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×3 + ④ ×2)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">لوحة الموارد البشرية</t>
+          <t xml:space="preserve">الأعمال غير المفوترة</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">employees/hr_board</t>
+          <t xml:space="preserve">operations/unbilled</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">ورقةُ DEP-07 — إدارة الموارد البشرية</t>
+          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
+          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
         </is>
       </c>
     </row>
@@ -6709,12 +6709,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">مستندات الموظف</t>
+          <t xml:space="preserve">لوحة الموارد البشرية</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">employees/hr_employee_documents</t>
+          <t xml:space="preserve">employees/hr_board</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">التهيئة والمباشرة</t>
+          <t xml:space="preserve">مستندات الموظف</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">employees/hr_onboarding</t>
+          <t xml:space="preserve">employees/hr_employee_documents</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">الحركات الوظيفية</t>
+          <t xml:space="preserve">التهيئة والمباشرة</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">employees/hr_job_movements</t>
+          <t xml:space="preserve">employees/hr_onboarding</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">التدريب والكفاءة</t>
+          <t xml:space="preserve">الحركات الوظيفية</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">employees/hr_training</t>
+          <t xml:space="preserve">employees/hr_job_movements</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6877,12 +6877,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">تقييم الأداء الوظيفي</t>
+          <t xml:space="preserve">التدريب والكفاءة</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">employees/hr_performance</t>
+          <t xml:space="preserve">employees/hr_training</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">القضايا التأديبية والتحقيق</t>
+          <t xml:space="preserve">تقييم الأداء الوظيفي</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">employees/hr_disciplinary</t>
+          <t xml:space="preserve">employees/hr_performance</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">تقرير القوى العاملة</t>
+          <t xml:space="preserve">القضايا التأديبية والتحقيق</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">workforce/hr_workforce_report</t>
+          <t xml:space="preserve">employees/hr_disciplinary</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">الموردون والمشتريات</t>
+          <t xml:space="preserve">الموظفون والمشغلون</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">طلبات الشراء</t>
+          <t xml:space="preserve">تقرير القوى العاملة</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">procurement/requests_proc</t>
+          <t xml:space="preserve">workforce/hr_workforce_report</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">ورقةُ DEP-16 — إدارة المشتريات التشغيلية</t>
+          <t xml:space="preserve">ورقةُ DEP-07 — إدارة الموارد البشرية</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">تجميع الطلبات وخطة الشراء</t>
+          <t xml:space="preserve">طلبات الشراء</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">procurement/proc_packages</t>
+          <t xml:space="preserve">procurement/requests_proc</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -7087,12 +7087,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">دعوات الموردين للعروض</t>
+          <t xml:space="preserve">تجميع الطلبات وخطة الشراء</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">procurement/proc_rfq</t>
+          <t xml:space="preserve">procurement/proc_packages</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -7119,22 +7119,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">المالية والمحاسبة</t>
+          <t xml:space="preserve">الموردون والمشتريات</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×7 + ⑤ ×1)</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">سجل الأدوات المالية</t>
+          <t xml:space="preserve">دعوات الموردين للعروض</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">finance/tre_instruments</t>
+          <t xml:space="preserve">procurement/proc_rfq</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">ورقةُ DEP-06 — إدارة الخزينة</t>
+          <t xml:space="preserve">ورقةُ DEP-16 — إدارة المشتريات التشغيلية</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">تخصيص التحصيل على الفواتير</t>
+          <t xml:space="preserve">سجل الأدوات المالية</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">finance/tre_allocations</t>
+          <t xml:space="preserve">finance/tre_instruments</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">مدفوعات معتمدة بانتظار التنفيذ</t>
+          <t xml:space="preserve">تخصيص التحصيل على الفواتير</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">finance/tre_payment_queue</t>
+          <t xml:space="preserve">finance/tre_allocations</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -7255,12 +7255,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">حركة الخزينة والصناديق</t>
+          <t xml:space="preserve">مدفوعات معتمدة بانتظار التنفيذ</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">finance/tre_cash_moves</t>
+          <t xml:space="preserve">finance/tre_payment_queue</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">التحويلات بين الحسابات</t>
+          <t xml:space="preserve">حركة الخزينة والصناديق</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">finance/tre_transfers</t>
+          <t xml:space="preserve">finance/tre_cash_moves</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -7339,12 +7339,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">عهد النثرية وتسويتها</t>
+          <t xml:space="preserve">التحويلات بين الحسابات</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">finance/tre_petty_cash</t>
+          <t xml:space="preserve">finance/tre_transfers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">الجرد النقدي للخزائن</t>
+          <t xml:space="preserve">عهد النثرية وتسويتها</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">finance/tre_cash_count</t>
+          <t xml:space="preserve">finance/tre_petty_cash</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7423,27 +7423,27 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">ميزانية إدارة التمويل</t>
+          <t xml:space="preserve">الجرد النقدي للخزائن</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">finance/budget_dept</t>
+          <t xml:space="preserve">finance/tre_cash_count</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
+          <t xml:space="preserve">ورقةُ DEP-06 — إدارة الخزينة</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
+          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
         </is>
       </c>
     </row>
@@ -7455,37 +7455,37 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">الخزينة والتمويل</t>
+          <t xml:space="preserve">المالية والمحاسبة</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×7 + ⑤ ×1)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">جهات اتصال الممولين والمفوض</t>
+          <t xml:space="preserve">ميزانية إدارة التمويل</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">financing/fin_financier_contacts</t>
+          <t xml:space="preserve">finance/budget_dept</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">ورقةُ DEP-03 — إدارة التمويل والممولين</t>
+          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
+          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
         </is>
       </c>
     </row>
@@ -7507,12 +7507,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">وثائق التأهيل والعناية</t>
+          <t xml:space="preserve">جهات اتصال الممولين والمفوض</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">financing/fin_due_diligence</t>
+          <t xml:space="preserve">financing/fin_financier_contacts</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">سجل عقود التمويل</t>
+          <t xml:space="preserve">وثائق التأهيل والعناية</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">financing/fin_contracts</t>
+          <t xml:space="preserve">financing/fin_due_diligence</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">بنود وشروط التمويل</t>
+          <t xml:space="preserve">سجل عقود التمويل</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">financing/fin_contract_terms</t>
+          <t xml:space="preserve">financing/fin_contracts</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7633,12 +7633,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">مصفوفة الالتزامات التمويلية</t>
+          <t xml:space="preserve">بنود وشروط التمويل</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">financing/fin_covenants</t>
+          <t xml:space="preserve">financing/fin_contract_terms</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">الحوكمة والتدقيق</t>
+          <t xml:space="preserve">الخزينة والتمويل</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7675,12 +7675,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">لوحة الحوكمة والالتزام</t>
+          <t xml:space="preserve">مصفوفة الالتزامات التمويلية</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">governance/gov_board</t>
+          <t xml:space="preserve">financing/fin_covenants</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">ورقةُ DEP-08 — إدارة الحوكمة والالتزام</t>
+          <t xml:space="preserve">ورقةُ DEP-03 — إدارة التمويل والممولين</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">سجل الشركات والكيانات</t>
+          <t xml:space="preserve">لوحة الحوكمة والالتزام</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">governance/entities_registry</t>
+          <t xml:space="preserve">governance/gov_board</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7759,12 +7759,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">سجل السياسات</t>
+          <t xml:space="preserve">سجل الشركات والكيانات</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">governance/policies</t>
+          <t xml:space="preserve">governance/entities_registry</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">سجل الالتزامات التنظيمية</t>
+          <t xml:space="preserve">سجل السياسات</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">governance/obligations</t>
+          <t xml:space="preserve">governance/policies</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">تقويم الامتثال</t>
+          <t xml:space="preserve">سجل الالتزامات التنظيمية</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">governance/compliance_calendar</t>
+          <t xml:space="preserve">governance/obligations</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">التفويض بالتوقيع</t>
+          <t xml:space="preserve">تقويم الامتثال</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">governance/signing_authority</t>
+          <t xml:space="preserve">governance/compliance_calendar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -7927,12 +7927,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">التقديمات النظامية</t>
+          <t xml:space="preserve">التفويض بالتوقيع</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">governance/regulatory_filings</t>
+          <t xml:space="preserve">governance/signing_authority</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -7959,22 +7959,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">المخاطر والبلاغات</t>
+          <t xml:space="preserve">الحوكمة والتدقيق</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×1 + ⑤ ×1)</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">صندوق بلاغات الإدارة</t>
+          <t xml:space="preserve">التقديمات النظامية</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">tickets/tickets_list</t>
+          <t xml:space="preserve">governance/regulatory_filings</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">ورقةُ DEP-10 — إدارة البلاغات</t>
+          <t xml:space="preserve">ورقةُ DEP-08 — إدارة الحوكمة والالتزام</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8011,27 +8011,27 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">مساحة مخاطر الإدارة</t>
+          <t xml:space="preserve">صندوق بلاغات الإدارة</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">risk/dept_risk_space</t>
+          <t xml:space="preserve">tickets/tickets_list</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
+          <t xml:space="preserve">ورقةُ DEP-10 — إدارة البلاغات</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
+          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
         </is>
       </c>
     </row>
@@ -8043,37 +8043,37 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">التقارير والتحليلات</t>
+          <t xml:space="preserve">المخاطر والبلاغات</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×7 + ⑤ ×3)</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×1 + ⑤ ×1)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">أرصدة المخزون بحالاتها</t>
+          <t xml:space="preserve">مساحة مخاطر الإدارة</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">procurement/stock_proc</t>
+          <t xml:space="preserve">risk/dept_risk_space</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">ورقةُ DEP-17 — إدارة المخازن</t>
+          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
+          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
         </is>
       </c>
     </row>
@@ -8095,27 +8095,27 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">الاعتمادات المتأخرة والوثائق</t>
+          <t xml:space="preserve">أرصدة المخزون بحالاتها</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">reports/approval_lag_report</t>
+          <t xml:space="preserve">procurement/stock_proc</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
+          <t xml:space="preserve">ورقةُ DEP-17 — إدارة المخازن</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
+          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
         </is>
       </c>
     </row>
@@ -8137,12 +8137,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">مركز تقارير الحوكمة</t>
+          <t xml:space="preserve">الاعتمادات المتأخرة والوثائق</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">emsreports/index</t>
+          <t xml:space="preserve">reports/approval_lag_report</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">لوحة مدير التشغيل</t>
+          <t xml:space="preserve">مركز تقارير الحوكمة</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin/ops_manager_board</t>
+          <t xml:space="preserve">emsreports/index</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -8221,27 +8221,27 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">لوحة النائب</t>
+          <t xml:space="preserve">لوحة مدير التشغيل</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">portal/vp_dashboard</t>
+          <t xml:space="preserve">admin/ops_manager_board</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">ورقةُ EX-DVP — مساحة نائب الرئيس</t>
+          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
+          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
         </is>
       </c>
     </row>
@@ -8263,12 +8263,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">الإدارات — نطاقي والشركة</t>
+          <t xml:space="preserve">لوحة النائب</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">portal/vp_departments</t>
+          <t xml:space="preserve">portal/vp_dashboard</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -8305,12 +8305,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">صندوق اعتمادات النائب</t>
+          <t xml:space="preserve">الإدارات — نطاقي والشركة</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">portal/vp_approval_inbox</t>
+          <t xml:space="preserve">portal/vp_departments</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">الإجراءات والقرارات المطلوبة مني</t>
+          <t xml:space="preserve">صندوق اعتمادات النائب</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">portal/vp_pending_actions</t>
+          <t xml:space="preserve">portal/vp_approval_inbox</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">طلب إدخال الأصل</t>
+          <t xml:space="preserve">الإجراءات والقرارات المطلوبة مني</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">fleet/asset_intake</t>
+          <t xml:space="preserve">portal/vp_pending_actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">ورقةُ DEP-04 — إدارة الأسطول والأصول</t>
+          <t xml:space="preserve">ورقةُ EX-DVP — مساحة نائب الرئيس</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">التخصيص على الوحدات</t>
+          <t xml:space="preserve">طلب إدخال الأصل</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">fleet/asset_assignments</t>
+          <t xml:space="preserve">fleet/asset_intake</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -8463,22 +8463,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">الإعدادات</t>
+          <t xml:space="preserve">التقارير والتحليلات</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×3 + ④ ×1)</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×7 + ⑤ ×3)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">أنماط تفعيل المزايا</t>
+          <t xml:space="preserve">التخصيص على الوحدات</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">governance/activation_patterns</t>
+          <t xml:space="preserve">fleet/asset_assignments</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">ورقةُ DEP-08 — إدارة الحوكمة والالتزام</t>
+          <t xml:space="preserve">ورقةُ DEP-04 — إدارة الأسطول والأصول</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -8515,27 +8515,27 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">التكليفات التنظيمية</t>
+          <t xml:space="preserve">أنماط تفعيل المزايا</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin/org_assignments</t>
+          <t xml:space="preserve">governance/activation_patterns</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
+          <t xml:space="preserve">ورقةُ DEP-08 — إدارة الحوكمة والالتزام</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
+          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
         </is>
       </c>
     </row>
@@ -8557,12 +8557,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">أذون الزيارة والمركبات الخارجية</t>
+          <t xml:space="preserve">التكليفات التنظيمية</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin/org_permits</t>
+          <t xml:space="preserve">admin/org_assignments</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -8599,25 +8599,67 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t xml:space="preserve">أذون الزيارة والمركبات الخارجية</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin/org_permits</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الإعدادات</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×3 + ④ ×1)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
           <t xml:space="preserve">إدارة المعاونين</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t xml:space="preserve">main/project_users</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
         </is>
@@ -13028,7 +13070,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×3 + ⑤ ×2)</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×4 + ⑤ ×2)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -13070,17 +13112,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×3 + ⑤ ×2)</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×4 + ⑤ ×2)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">الحضور والانصراف</t>
+          <t xml:space="preserve">قرارات الهيكل التنظيمي</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">operations/attendance</t>
+          <t xml:space="preserve">portal/ceo_org_decisions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -13090,7 +13132,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ورقةُ DEP-07 — إدارة الموارد البشرية</t>
+          <t xml:space="preserve">ورقةُ EX-CEO — مساحة الرئيس التنفيذي</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -13112,17 +13154,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×3 + ⑤ ×2)</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×4 + ⑤ ×2)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">سجل ساعات التشغيل اليومي</t>
+          <t xml:space="preserve">الحضور والانصراف</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">timesheet/timesheet</t>
+          <t xml:space="preserve">operations/attendance</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -13132,7 +13174,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">ورقةُ DEP-11 — إدارة التشغيل</t>
+          <t xml:space="preserve">ورقةُ DEP-07 — إدارة الموارد البشرية</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -13154,32 +13196,32 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×3 + ⑤ ×2)</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×4 + ⑤ ×2)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">تكليف المشغل على المعدة</t>
+          <t xml:space="preserve">سجل ساعات التشغيل اليومي</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">operations/distribution_space</t>
+          <t xml:space="preserve">timesheet/timesheet</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
+          <t xml:space="preserve">ورقةُ DEP-11 — إدارة التشغيل</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
+          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
         </is>
       </c>
     </row>
@@ -13196,17 +13238,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×3 + ⑤ ×2)</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×4 + ⑤ ×2)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">سجل الوردية</t>
+          <t xml:space="preserve">تكليف المشغل على المعدة</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">operations/shift_log</t>
+          <t xml:space="preserve">operations/distribution_space</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -13233,22 +13275,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">الموظفون والمشغلون</t>
+          <t xml:space="preserve">التشغيل اليومي</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×6 + ④ ×6)</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×4 + ⑤ ×2)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">الأداء الشهري للمشغل</t>
+          <t xml:space="preserve">سجل الوردية</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">workforce/op_monthly</t>
+          <t xml:space="preserve">operations/shift_log</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -13285,12 +13327,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">أرقام المشغلين الشاغرة</t>
+          <t xml:space="preserve">الأداء الشهري للمشغل</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">workforce/op_codes</t>
+          <t xml:space="preserve">workforce/op_monthly</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -13327,12 +13369,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">تأهيل المشغلين على أنواع المعدات</t>
+          <t xml:space="preserve">أرقام المشغلين الشاغرة</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">workforce/op_qual</t>
+          <t xml:space="preserve">workforce/op_codes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -13369,12 +13411,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">خصومات المشغلين المقترحة</t>
+          <t xml:space="preserve">تأهيل المشغلين على أنواع المعدات</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">workforce/proposed_deductions</t>
+          <t xml:space="preserve">workforce/op_qual</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -13411,27 +13453,27 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">التوظيف من الشاغر إلى المباشرة</t>
+          <t xml:space="preserve">خصومات المشغلين المقترحة</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">workforce/recruitment_pipeline</t>
+          <t xml:space="preserve">workforce/proposed_deductions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ورقةُ DEP-07 — إدارة الموارد البشرية</t>
+          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
+          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
         </is>
       </c>
     </row>
@@ -13453,12 +13495,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">طلبات الترشح</t>
+          <t xml:space="preserve">التوظيف من الشاغر إلى المباشرة</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">workforce/rec_applications</t>
+          <t xml:space="preserve">workforce/recruitment_pipeline</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -13495,12 +13537,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">مراحل التوظيف</t>
+          <t xml:space="preserve">طلبات الترشح</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">workforce/rec_stages</t>
+          <t xml:space="preserve">workforce/rec_applications</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -13537,12 +13579,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">عقود المشاريع المؤقتة</t>
+          <t xml:space="preserve">مراحل التوظيف</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">workforce/project_contracts</t>
+          <t xml:space="preserve">workforce/rec_stages</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -13579,12 +13621,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">الإجازات والغياب</t>
+          <t xml:space="preserve">عقود المشاريع المؤقتة</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">workforce/worker_leave_absence</t>
+          <t xml:space="preserve">workforce/project_contracts</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -13621,12 +13663,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">خصومات المسيّر</t>
+          <t xml:space="preserve">الإجازات والغياب</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">workforce/deductions</t>
+          <t xml:space="preserve">workforce/worker_leave_absence</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -13663,27 +13705,27 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">دورات التناوب والإجازة الميدانية</t>
+          <t xml:space="preserve">خصومات المسيّر</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">workforce/rotation</t>
+          <t xml:space="preserve">workforce/deductions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
+          <t xml:space="preserve">ورقةُ DEP-07 — إدارة الموارد البشرية</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
+          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13747,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">تنقلات العاملين</t>
+          <t xml:space="preserve">دورات التناوب والإجازة الميدانية</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">workforce/worker_movement</t>
+          <t xml:space="preserve">workforce/rotation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -13737,22 +13779,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">المالية والمحاسبة</t>
+          <t xml:space="preserve">الموظفون والمشغلون</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم (مختلطٌ: ⑤ ×6 + ④ ×6)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">ميزانية إدارة التمويل</t>
+          <t xml:space="preserve">تنقلات العاملين</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">finance/budget_dept</t>
+          <t xml:space="preserve">workforce/worker_movement</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -13779,37 +13821,37 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">المخاطر والبلاغات</t>
+          <t xml:space="preserve">المالية والمحاسبة</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×2 + ⑤ ×1)</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">الإبلاغ السياقي من داخل الشاشة</t>
+          <t xml:space="preserve">ميزانية إدارة التمويل</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">tickets/ticket_contextual_open</t>
+          <t xml:space="preserve">finance/budget_dept</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">ورقةُ DEP-10 — إدارة البلاغات</t>
+          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
+          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
         </is>
       </c>
     </row>
@@ -13831,12 +13873,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">صندوق بلاغات الإدارة</t>
+          <t xml:space="preserve">الإبلاغ السياقي من داخل الشاشة</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">tickets/tickets_list</t>
+          <t xml:space="preserve">tickets/ticket_contextual_open</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -13873,27 +13915,27 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">مساحة مخاطر الإدارة</t>
+          <t xml:space="preserve">صندوق بلاغات الإدارة</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">risk/dept_risk_space</t>
+          <t xml:space="preserve">tickets/tickets_list</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
+          <t xml:space="preserve">ورقةُ DEP-10 — إدارة البلاغات</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
+          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
         </is>
       </c>
     </row>
@@ -13905,37 +13947,37 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">التقارير والتحليلات</t>
+          <t xml:space="preserve">المخاطر والبلاغات</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×4 + ⑤ ×1)</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×2 + ⑤ ×1)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">لوحة النائب</t>
+          <t xml:space="preserve">مساحة مخاطر الإدارة</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">portal/vp_dashboard</t>
+          <t xml:space="preserve">risk/dept_risk_space</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">ورقةُ EX-DVP — مساحة نائب الرئيس</t>
+          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
+          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
         </is>
       </c>
     </row>
@@ -13957,12 +13999,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">الإدارات — نطاقي والشركة</t>
+          <t xml:space="preserve">لوحة النائب</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">portal/vp_departments</t>
+          <t xml:space="preserve">portal/vp_dashboard</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -13999,12 +14041,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">صندوق اعتمادات النائب</t>
+          <t xml:space="preserve">الإدارات — نطاقي والشركة</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">portal/vp_approval_inbox</t>
+          <t xml:space="preserve">portal/vp_departments</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -14041,12 +14083,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">الإجراءات والقرارات المطلوبة مني</t>
+          <t xml:space="preserve">صندوق اعتمادات النائب</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">portal/vp_pending_actions</t>
+          <t xml:space="preserve">portal/vp_approval_inbox</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -14083,27 +14125,27 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">مركز تقارير الحوكمة</t>
+          <t xml:space="preserve">الإجراءات والقرارات المطلوبة مني</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">emsreports/index</t>
+          <t xml:space="preserve">portal/vp_pending_actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
+          <t xml:space="preserve">ورقةُ EX-DVP — مساحة نائب الرئيس</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
+          <t xml:space="preserve">يُراجَع — أتُبقى استعارةً أم تُخفى؟</t>
         </is>
       </c>
     </row>
@@ -14115,35 +14157,77 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t xml:space="preserve">التقارير والتحليلات</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">④ المستعارة — إدارةٌ أخرى (مختلطٌ: ④ ×4 + ⑤ ×1)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مركز تقارير الحوكمة</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emsreports/index</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t xml:space="preserve">الإعدادات</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t xml:space="preserve">إدارة المعاونين</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t xml:space="preserve">main/project_users</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
         </is>
@@ -24480,7 +24564,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin/org_structure</t>
+          <t xml:space="preserve">portal/ceo_org_decisions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -26239,12 +26323,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">التكليفات التنظيمية</t>
+          <t xml:space="preserve">الهيكل التنظيمي والمسميات</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin/org_assignments</t>
+          <t xml:space="preserve">admin/org_structure</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -26281,12 +26365,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">وضع التأسيس وإغلاقه</t>
+          <t xml:space="preserve">التكليفات التنظيمية</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">portal/founding_mode</t>
+          <t xml:space="preserve">admin/org_assignments</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -26323,12 +26407,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">بصمة الإصدار وتقرير النشر</t>
+          <t xml:space="preserve">وضع التأسيس وإغلاقه</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">portal/release_stamp</t>
+          <t xml:space="preserve">portal/founding_mode</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -26365,25 +26449,67 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">بصمة الإصدار وتقرير النشر</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">portal/release_stamp</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الإعدادات</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
           <t xml:space="preserve">إدارة المعاونين</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t xml:space="preserve">main/project_users</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t xml:space="preserve">⑤ الإرث — التصنيف القديم</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">التصنيفُ الاثنا عشرَ — سابقٌ للدليل</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t xml:space="preserve">يُحسَم — تُضاف للدليلِ أم تُخفى بحكم؟</t>
         </is>
